--- a/data/trans_orig/P57GLOBAL_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>754743</t>
+          <t>756153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>808685</t>
+          <t>809719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1010710</t>
+          <t>1010053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1071449</t>
+          <t>1066981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1784508</t>
+          <t>1784014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1862817</t>
+          <t>1861300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223038</t>
+          <t>222004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276980</t>
+          <t>275570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243664</t>
+          <t>248132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304403</t>
+          <t>305060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484018</t>
+          <t>485535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562327</t>
+          <t>562821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1106968</t>
+          <t>1105325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1185109</t>
+          <t>1186205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1055130</t>
+          <t>1051256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1127025</t>
+          <t>1123655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2183673</t>
+          <t>2183172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2296095</t>
+          <t>2290593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>506622</t>
+          <t>505526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584763</t>
+          <t>586406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457522</t>
+          <t>460892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>529417</t>
+          <t>533291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>980183</t>
+          <t>985685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1092605</t>
+          <t>1093106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351595</t>
+          <t>351067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>397041</t>
+          <t>396001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>286456</t>
+          <t>285240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>328722</t>
+          <t>327157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>651417</t>
+          <t>652789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>713696</t>
+          <t>714166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149981</t>
+          <t>151021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>195427</t>
+          <t>195955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147690</t>
+          <t>149255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189956</t>
+          <t>191172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309738</t>
+          <t>309268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372017</t>
+          <t>370645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2250542</t>
+          <t>2250039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2354164</t>
+          <t>2355032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2385333</t>
+          <t>2385562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2485211</t>
+          <t>2491086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4661791</t>
+          <t>4665905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4811229</t>
+          <t>4815066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916312</t>
+          <t>915444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019934</t>
+          <t>1020437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>890860</t>
+          <t>884985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>990738</t>
+          <t>990509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835319</t>
+          <t>1831482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1984757</t>
+          <t>1980643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>666077</t>
+          <t>665493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>720661</t>
+          <t>722463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>993434</t>
+          <t>992488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1053395</t>
+          <t>1051148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1676724</t>
+          <t>1670823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1757728</t>
+          <t>1758628</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234457</t>
+          <t>232655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289041</t>
+          <t>289625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268013</t>
+          <t>270260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327974</t>
+          <t>328920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518797</t>
+          <t>517897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>599801</t>
+          <t>605702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1266977</t>
+          <t>1263295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1351536</t>
+          <t>1346422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1282770</t>
+          <t>1282843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1355666</t>
+          <t>1355890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2572359</t>
+          <t>2570398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2686096</t>
+          <t>2684162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>596482</t>
+          <t>601596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681041</t>
+          <t>684723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389525</t>
+          <t>389301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462421</t>
+          <t>462348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007113</t>
+          <t>1009047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1120850</t>
+          <t>1122811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>301758</t>
+          <t>297588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>344967</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>283888</t>
+          <t>284078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>326283</t>
+          <t>324293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>594851</t>
+          <t>597037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>655264</t>
+          <t>658482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131252</t>
+          <t>135908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174461</t>
+          <t>178631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125943</t>
+          <t>127933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168338</t>
+          <t>168148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>273181</t>
+          <t>269963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>333594</t>
+          <t>331408</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2270100</t>
+          <t>2270364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2386346</t>
+          <t>2376428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2594601</t>
+          <t>2595216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2704541</t>
+          <t>2702607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4893206</t>
+          <t>4900532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5049398</t>
+          <t>5052851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>993009</t>
+          <t>1002927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1109255</t>
+          <t>1108991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>814284</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>924224</t>
+          <t>923609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848781</t>
+          <t>1845328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2004973</t>
+          <t>1997647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016 (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>592137</t>
+          <t>589557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>633259</t>
+          <t>631700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>843124</t>
+          <t>841709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>886539</t>
+          <t>887033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1448641</t>
+          <t>1449065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1507697</t>
+          <t>1509815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115253</t>
+          <t>116812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156375</t>
+          <t>158955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99572</t>
+          <t>99078</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142987</t>
+          <t>144402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226926</t>
+          <t>224808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285982</t>
+          <t>285558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1679815</t>
+          <t>1681050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1747256</t>
+          <t>1748070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1658025</t>
+          <t>1656559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1720697</t>
+          <t>1717600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3359276</t>
+          <t>3354214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3448303</t>
+          <t>3448794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311438</t>
+          <t>310624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>378879</t>
+          <t>377644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249664</t>
+          <t>252761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312336</t>
+          <t>313802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580752</t>
+          <t>580261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>669779</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>394587</t>
+          <t>395341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>436677</t>
+          <t>437077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>389387</t>
+          <t>386826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427495</t>
+          <t>426866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>799271</t>
+          <t>794588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>855456</t>
+          <t>851957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107376</t>
+          <t>106976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149466</t>
+          <t>148712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112355</t>
+          <t>112984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150463</t>
+          <t>153024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228448</t>
+          <t>231947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284633</t>
+          <t>289316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2700372</t>
+          <t>2697468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2785047</t>
+          <t>2789583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2920744</t>
+          <t>2917427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3006130</t>
+          <t>3003380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5643807</t>
+          <t>5641527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5771006</t>
+          <t>5767447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>566213</t>
+          <t>561677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650888</t>
+          <t>653792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490193</t>
+          <t>492943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>575579</t>
+          <t>578896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1076576</t>
+          <t>1080135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1203775</t>
+          <t>1206055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023 (tasa de respuesta: 98,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317139</t>
+          <t>315299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>358399</t>
+          <t>358166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>501582</t>
+          <t>501234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>538400</t>
+          <t>539567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>828092</t>
+          <t>830907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>885582</t>
+          <t>883013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144172</t>
+          <t>144405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185432</t>
+          <t>187272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191246</t>
+          <t>190079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228064</t>
+          <t>228412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346635</t>
+          <t>349204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>404125</t>
+          <t>401310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>825443</t>
+          <t>868268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1433521</t>
+          <t>1441505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1066341</t>
+          <t>1086380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1292967</t>
+          <t>1295955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1981796</t>
+          <t>1959305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2679279</t>
+          <t>2687620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,95%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>834070</t>
+          <t>826086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1442148</t>
+          <t>1399323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>708732</t>
+          <t>705744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>935358</t>
+          <t>915319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1590011</t>
+          <t>1581670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2287494</t>
+          <t>2309985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362056</t>
+          <t>356766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>415032</t>
+          <t>410580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>350199</t>
+          <t>350477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>392358</t>
+          <t>394719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>726703</t>
+          <t>723192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>794880</t>
+          <t>794249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>218693</t>
+          <t>223145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271669</t>
+          <t>276959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>262936</t>
+          <t>260575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305095</t>
+          <t>304817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>494139</t>
+          <t>494770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>562316</t>
+          <t>565827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1461251</t>
+          <t>1460127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2164884</t>
+          <t>2166149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1949602</t>
+          <t>1940528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2185378</t>
+          <t>2193395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3488230</t>
+          <t>3604878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4298245</t>
+          <t>4311230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1239003</t>
+          <t>1237738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1942636</t>
+          <t>1943760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1201261</t>
+          <t>1193244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1437037</t>
+          <t>1446111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2492280</t>
+          <t>2479295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3302295</t>
+          <t>3185647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57GLOBAL_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>756153</t>
+          <t>751281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>809719</t>
+          <t>808253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1010053</t>
+          <t>1013499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1066981</t>
+          <t>1071707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1784014</t>
+          <t>1785190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1861300</t>
+          <t>1865522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222004</t>
+          <t>223470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275570</t>
+          <t>280442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248132</t>
+          <t>243406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305060</t>
+          <t>301614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485535</t>
+          <t>481313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562821</t>
+          <t>561645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1105325</t>
+          <t>1105684</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1186205</t>
+          <t>1184045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1051256</t>
+          <t>1052276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1123655</t>
+          <t>1131291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2183172</t>
+          <t>2184328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2290593</t>
+          <t>2287948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505526</t>
+          <t>507686</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>586406</t>
+          <t>586047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>460892</t>
+          <t>453256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>533291</t>
+          <t>532271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>985685</t>
+          <t>988330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1093106</t>
+          <t>1091950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351067</t>
+          <t>353469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>396001</t>
+          <t>397981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>285240</t>
+          <t>285825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>327157</t>
+          <t>328329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>652789</t>
+          <t>651839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>714166</t>
+          <t>713252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151021</t>
+          <t>149041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>195955</t>
+          <t>193553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149255</t>
+          <t>148083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191172</t>
+          <t>190587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309268</t>
+          <t>310182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>370645</t>
+          <t>371595</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2250039</t>
+          <t>2246459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2355032</t>
+          <t>2354550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2385562</t>
+          <t>2391150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2491086</t>
+          <t>2493440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4665905</t>
+          <t>4670773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4815066</t>
+          <t>4816316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915444</t>
+          <t>915926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1020437</t>
+          <t>1024017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>884985</t>
+          <t>882631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>990509</t>
+          <t>984921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1831482</t>
+          <t>1830232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1980643</t>
+          <t>1975775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>665493</t>
+          <t>664724</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>722463</t>
+          <t>722912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992488</t>
+          <t>990917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1051148</t>
+          <t>1053627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1670823</t>
+          <t>1673276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1758628</t>
+          <t>1755263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232655</t>
+          <t>232206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289625</t>
+          <t>290394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270260</t>
+          <t>267781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>328920</t>
+          <t>330491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517897</t>
+          <t>521262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>605702</t>
+          <t>603249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1263295</t>
+          <t>1266595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1346422</t>
+          <t>1350020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1282843</t>
+          <t>1283330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1355890</t>
+          <t>1355288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2570398</t>
+          <t>2567747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2684162</t>
+          <t>2683530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>601596</t>
+          <t>597998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684723</t>
+          <t>681423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389301</t>
+          <t>389903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462348</t>
+          <t>461861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009047</t>
+          <t>1009679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1122811</t>
+          <t>1125462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>297588</t>
+          <t>299643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>340311</t>
+          <t>344396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>284078</t>
+          <t>283363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>324293</t>
+          <t>328308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>597037</t>
+          <t>596161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>658482</t>
+          <t>657700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135908</t>
+          <t>131823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>178631</t>
+          <t>176576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127933</t>
+          <t>123918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168148</t>
+          <t>168863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269963</t>
+          <t>270745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331408</t>
+          <t>332284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2270364</t>
+          <t>2270286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2376428</t>
+          <t>2377566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2595216</t>
+          <t>2593910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2702607</t>
+          <t>2699627</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4900532</t>
+          <t>4903403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5052851</t>
+          <t>5050165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1002927</t>
+          <t>1001789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1108991</t>
+          <t>1109069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>819198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>923609</t>
+          <t>924915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1845328</t>
+          <t>1848014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1997647</t>
+          <t>1994776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>589557</t>
+          <t>592350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>631700</t>
+          <t>633970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>841709</t>
+          <t>844338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>887033</t>
+          <t>884078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1449065</t>
+          <t>1450387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1509815</t>
+          <t>1510012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116812</t>
+          <t>114542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158955</t>
+          <t>156162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99078</t>
+          <t>102033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144402</t>
+          <t>141773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224808</t>
+          <t>224611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285558</t>
+          <t>284236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1681050</t>
+          <t>1678483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1748070</t>
+          <t>1747027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1656559</t>
+          <t>1660037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1717600</t>
+          <t>1721163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3354214</t>
+          <t>3354460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3448794</t>
+          <t>3446916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310624</t>
+          <t>311667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377644</t>
+          <t>380211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252761</t>
+          <t>249198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313802</t>
+          <t>310324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580261</t>
+          <t>582139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>674595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>395341</t>
+          <t>395293</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>437077</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386826</t>
+          <t>388234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>426866</t>
+          <t>429164</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>794588</t>
+          <t>799215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>851957</t>
+          <t>853758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106976</t>
+          <t>105975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148712</t>
+          <t>148760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112984</t>
+          <t>110686</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153024</t>
+          <t>151616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231947</t>
+          <t>230146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>289316</t>
+          <t>284689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2697468</t>
+          <t>2700113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2789583</t>
+          <t>2789519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2917427</t>
+          <t>2920575</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3003380</t>
+          <t>3004631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5641527</t>
+          <t>5639553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5767447</t>
+          <t>5761948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561677</t>
+          <t>561741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>653792</t>
+          <t>651147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>492943</t>
+          <t>491692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578896</t>
+          <t>575748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1080135</t>
+          <t>1085634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1206055</t>
+          <t>1208029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>337137</t>
+          <t>382152</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>315299</t>
+          <t>358399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>358166</t>
+          <t>405179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>520029</t>
+          <t>573544</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>501234</t>
+          <t>553571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>539567</t>
+          <t>591168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>857166</t>
+          <t>955696</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>830907</t>
+          <t>924818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>883013</t>
+          <t>982842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,31%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>165434</t>
+          <t>183526</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144405</t>
+          <t>160499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187272</t>
+          <t>207279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>209617</t>
+          <t>219936</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>190079</t>
+          <t>202312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228412</t>
+          <t>239909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>375051</t>
+          <t>403462</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>349204</t>
+          <t>376316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>401310</t>
+          <t>434340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>502571</t>
+          <t>565678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>502571</t>
+          <t>565678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>502571</t>
+          <t>565678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>729646</t>
+          <t>793480</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>729646</t>
+          <t>793480</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>729646</t>
+          <t>793480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1232217</t>
+          <t>1359158</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1232217</t>
+          <t>1359158</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1232217</t>
+          <t>1359158</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1267954</t>
+          <t>1416484</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>868268</t>
+          <t>1362894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1441505</t>
+          <t>1470397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1225904</t>
+          <t>1396466</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1086380</t>
+          <t>1353613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1295955</t>
+          <t>1435161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2493858</t>
+          <t>2812950</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1959305</t>
+          <t>2744018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2687620</t>
+          <t>2875714</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>999637</t>
+          <t>789503</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>826086</t>
+          <t>735590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1399323</t>
+          <t>843093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>775795</t>
+          <t>740927</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705744</t>
+          <t>702232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>915319</t>
+          <t>783780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1775432</t>
+          <t>1530430</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1581670</t>
+          <t>1467666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2309985</t>
+          <t>1599362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2267591</t>
+          <t>2205987</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2267591</t>
+          <t>2205987</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2267591</t>
+          <t>2205987</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2001699</t>
+          <t>2137393</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2001699</t>
+          <t>2137393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2001699</t>
+          <t>2137393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4269290</t>
+          <t>4343380</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4269290</t>
+          <t>4343380</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4269290</t>
+          <t>4343380</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>386267</t>
+          <t>431481</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>356766</t>
+          <t>403393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>410580</t>
+          <t>459684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>372195</t>
+          <t>419772</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>350477</t>
+          <t>397026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>394719</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>758463</t>
+          <t>851253</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>723192</t>
+          <t>812872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>794249</t>
+          <t>889187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>247458</t>
+          <t>265843</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>223145</t>
+          <t>237640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276959</t>
+          <t>293931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>283099</t>
+          <t>307893</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260575</t>
+          <t>281953</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>304817</t>
+          <t>330639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>530556</t>
+          <t>573736</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>494770</t>
+          <t>535802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>565827</t>
+          <t>612117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>633725</t>
+          <t>697324</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>633725</t>
+          <t>697324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>633725</t>
+          <t>697324</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>655294</t>
+          <t>727665</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>655294</t>
+          <t>727665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>655294</t>
+          <t>727665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1289019</t>
+          <t>1424989</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1289019</t>
+          <t>1424989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1289019</t>
+          <t>1424989</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1991359</t>
+          <t>2230116</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1460127</t>
+          <t>2162014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2166149</t>
+          <t>2290971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2118128</t>
+          <t>2389782</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1940528</t>
+          <t>2332910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2193395</t>
+          <t>2442468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4109486</t>
+          <t>4619899</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3604878</t>
+          <t>4536736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4311230</t>
+          <t>4707324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1412528</t>
+          <t>1238873</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1237738</t>
+          <t>1178018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1943760</t>
+          <t>1306975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1268511</t>
+          <t>1268756</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1193244</t>
+          <t>1216070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1446111</t>
+          <t>1325628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2681039</t>
+          <t>2507628</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2479295</t>
+          <t>2420203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3185647</t>
+          <t>2590791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3403887</t>
+          <t>3468989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3403887</t>
+          <t>3468989</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3403887</t>
+          <t>3468989</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3386639</t>
+          <t>3658538</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3386639</t>
+          <t>3658538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3386639</t>
+          <t>3658538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6790525</t>
+          <t>7127527</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6790525</t>
+          <t>7127527</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6790525</t>
+          <t>7127527</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
